--- a/real_estate_forms/046_grant_deed_form--real_estate_forms.xlsx
+++ b/real_estate_forms/046_grant_deed_form--real_estate_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Grantee Name</t>
+          <t>Grantee Name 1</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1031,7 +1031,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Grantor Name</t>
+          <t>Grantor Name 1</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Grantor Address</t>
+          <t>Grantor Address 1</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Grantee Address</t>
+          <t>Grantee Address 1</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1098,7 +1098,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>amador_county</t>
+          <t>alpine_county</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Amador County</t>
+          <t>Alpine County</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>alpine_county</t>
+          <t>alturas_county</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Alpine County</t>
+          <t>Alturas County</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>alturas_county</t>
+          <t>amarillo_county</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Alturas County</t>
+          <t>Amarillo County</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>amarillo_county</t>
+          <t>amherst_county</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Amarillo County</t>
+          <t>Amherst County</t>
         </is>
       </c>
     </row>
@@ -1284,29 +1284,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>amherst_county</t>
+          <t>anaconda_county</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Amherst County</t>
+          <t>Anaconda County</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>county_name_choices</t>
+          <t>state_abbreviation_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>anaconda_county</t>
+          <t>al</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Anaconda County</t>
+          <t>AL</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>al</t>
+          <t>ak</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>AK</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ak</t>
+          <t>am</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>AK</t>
+          <t>AM</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>am</t>
+          <t>ap</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>AM</t>
+          <t>AP</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ap</t>
+          <t>ar</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AP</t>
+          <t>AR</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ar</t>
+          <t>as</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>AS</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>as</t>
+          <t>at</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AS</t>
+          <t>AT</t>
         </is>
       </c>
     </row>
@@ -1420,29 +1420,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>at</t>
+          <t>au</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AT</t>
+          <t>AU</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>state_abbreviation_choices</t>
+          <t>consideration_method_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>au</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1454,27 +1454,10 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>consideration_method_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
         <is>
           <t>No</t>
         </is>
